--- a/artfynd/A 14601-2023 artfynd.xlsx
+++ b/artfynd/A 14601-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14601-2023 artfynd.xlsx
+++ b/artfynd/A 14601-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1454,6 +1454,237 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122859531</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnsved, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618434</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6716467</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122872010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56787</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Finnsved, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618434</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6716467</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14601-2023 artfynd.xlsx
+++ b/artfynd/A 14601-2023 artfynd.xlsx
@@ -1457,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122859531</v>
+        <v>122872010</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>56787</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,33 +1469,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnsved, Gstr</t>
@@ -1535,19 +1542,9 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,10 +1571,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122872010</v>
+        <v>122859531</v>
       </c>
       <c r="B9" t="n">
-        <v>56787</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,40 +1583,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnsved, Gstr</t>
@@ -1659,9 +1649,19 @@
           <t>2025-03-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14601-2023 artfynd.xlsx
+++ b/artfynd/A 14601-2023 artfynd.xlsx
@@ -1457,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122872010</v>
+        <v>122859531</v>
       </c>
       <c r="B8" t="n">
-        <v>56787</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,40 +1469,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnsved, Gstr</t>
@@ -1542,9 +1535,19 @@
           <t>2025-03-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,10 +1574,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122859531</v>
+        <v>122872010</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>56787</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1583,33 +1586,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100038</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnsved, Gstr</t>
@@ -1649,19 +1659,9 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14601-2023 artfynd.xlsx
+++ b/artfynd/A 14601-2023 artfynd.xlsx
@@ -1457,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122859531</v>
+        <v>122872010</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>56790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,33 +1469,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnsved, Gstr</t>
@@ -1535,19 +1542,9 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,10 +1571,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122872010</v>
+        <v>122859531</v>
       </c>
       <c r="B9" t="n">
-        <v>56787</v>
+        <v>57634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,40 +1583,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnsved, Gstr</t>
@@ -1659,9 +1649,19 @@
           <t>2025-03-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
